--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{474E1292-4977-4751-8F4B-C4302231AE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F48ADB-6F84-4BC6-94E6-E96DBA10B807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -439,18 +439,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -458,8 +461,11 @@
         <f>A2*0.6+(100-A2)</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -468,7 +474,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -477,7 +483,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -486,7 +492,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -495,7 +501,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -504,7 +510,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F48ADB-6F84-4BC6-94E6-E96DBA10B807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="4818" yWindow="198" windowWidth="7549" windowHeight="7722" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -439,10 +439,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -452,8 +452,11 @@
       <c r="E1">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -465,7 +468,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -473,8 +476,11 @@
         <f t="shared" ref="B3:B8" si="0">A3*0.6+(100-A3)</f>
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="E3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -483,7 +489,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -492,7 +498,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -501,7 +507,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -510,7 +516,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EACFD27-3543-4F33-86C7-E6B2397238D5}"/>
   <bookViews>
-    <workbookView xWindow="4818" yWindow="198" windowWidth="7549" windowHeight="7722" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -439,10 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="5" max="9" width="5.3046875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,8 +458,17 @@
       <c r="F1">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1">
+        <v>1</v>
+      </c>
+      <c r="H1">
+        <v>2</v>
+      </c>
+      <c r="I1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -467,8 +479,11 @@
       <c r="E2">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="F2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -480,7 +495,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -489,7 +504,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -498,7 +513,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -507,7 +522,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -516,13 +531,35 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
         <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="E12">
+        <f>AVERAGE(E2:E11)</f>
+        <v>85</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12:I12" si="1">AVERAGE(F2:F11)</f>
+        <v>75</v>
+      </c>
+      <c r="G12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I12" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EACFD27-3543-4F33-86C7-E6B2397238D5}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A636934-8AEE-4A0C-AF4C-019A23C4E3CC}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -120,6 +120,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,6 +498,9 @@
       <c r="E3">
         <v>90</v>
       </c>
+      <c r="F3">
+        <v>70</v>
+      </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
@@ -547,7 +554,7 @@
       </c>
       <c r="F12">
         <f t="shared" ref="F12:I12" si="1">AVERAGE(F2:F11)</f>
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="G12" t="e">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A636934-8AEE-4A0C-AF4C-019A23C4E3CC}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED9F4DC-7948-41E9-A034-064D852865C3}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -510,6 +510,9 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
+      <c r="F4" s="1">
+        <v>80</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -519,6 +522,9 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
+      <c r="F5">
+        <v>78</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -528,6 +534,9 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
+      <c r="F6">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -537,6 +546,9 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -545,6 +557,9 @@
       <c r="B8">
         <f t="shared" si="0"/>
         <v>76</v>
+      </c>
+      <c r="F8">
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
@@ -554,7 +569,7 @@
       </c>
       <c r="F12">
         <f t="shared" ref="F12:I12" si="1">AVERAGE(F2:F11)</f>
-        <v>72.5</v>
+        <v>78.285714285714292</v>
       </c>
       <c r="G12" t="e">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED9F4DC-7948-41E9-A034-064D852865C3}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2641A14C-A2D5-4FE7-9E76-72BD23A5F7B6}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -443,13 +443,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="9" width="5.3046875" customWidth="1"/>
+    <col min="5" max="6" width="5.3046875" customWidth="1"/>
+    <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -486,8 +487,20 @@
       <c r="F2">
         <v>75</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -502,7 +515,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -514,7 +527,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -526,7 +539,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -538,7 +551,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -550,7 +563,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -562,7 +575,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="E12">
         <f>AVERAGE(E2:E11)</f>
         <v>85</v>
@@ -571,17 +584,17 @@
         <f t="shared" ref="F12:I12" si="1">AVERAGE(F2:F11)</f>
         <v>78.285714285714292</v>
       </c>
-      <c r="G12" t="e">
+      <c r="G12">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H12" t="e">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I12" t="e">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{AA4341F0-D96C-40EA-B231-07DB4178F243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2641A14C-A2D5-4FE7-9E76-72BD23A5F7B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -120,10 +120,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,9 +440,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.3046875" customWidth="1"/>
+    <col min="5" max="6" width="5.28515625" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -575,6 +571,11 @@
         <v>75</v>
       </c>
     </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="F9">
+        <v>85</v>
+      </c>
+    </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="E12">
         <f>AVERAGE(E2:E11)</f>
@@ -582,7 +583,7 @@
       </c>
       <c r="F12">
         <f t="shared" ref="F12:I12" si="1">AVERAGE(F2:F11)</f>
-        <v>78.285714285714292</v>
+        <v>79.125</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F354986F-7046-42BC-90ED-A23B1169C9E7}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -440,9 +440,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.28515625" customWidth="1"/>
+    <col min="5" max="6" width="5.3046875" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -484,7 +484,7 @@
         <v>75</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -509,6 +509,9 @@
       </c>
       <c r="F3">
         <v>70</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -587,7 +590,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F354986F-7046-42BC-90ED-A23B1169C9E7}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67648C76-888D-4993-B3FD-6BCB91683AEC}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -525,6 +525,9 @@
       <c r="F4" s="1">
         <v>80</v>
       </c>
+      <c r="G4" s="1">
+        <v>65</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -536,6 +539,9 @@
       </c>
       <c r="F5">
         <v>78</v>
+      </c>
+      <c r="G5">
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67648C76-888D-4993-B3FD-6BCB91683AEC}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB85801E-693C-4838-8F8E-8FC49C00E3D1}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -555,6 +555,9 @@
       <c r="F6">
         <v>80</v>
       </c>
+      <c r="G6">
+        <v>70</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -596,7 +599,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB85801E-693C-4838-8F8E-8FC49C00E3D1}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D47B7961-E06A-40F9-BBC1-7CA782DC4FCE}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -120,6 +120,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,6 +574,9 @@
       <c r="F7">
         <v>90</v>
       </c>
+      <c r="G7">
+        <v>90</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -599,7 +606,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>74</v>
+        <v>76.666666666666671</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{CD29CE74-5EFE-4C46-A21B-76D4E8BE155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D47B7961-E06A-40F9-BBC1-7CA782DC4FCE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EE1CF4-6563-4953-ADDA-2D9EE991DAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -120,10 +120,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,9 +440,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.3046875" customWidth="1"/>
+    <col min="5" max="6" width="5.28515625" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -589,10 +585,21 @@
       <c r="F8">
         <v>75</v>
       </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="F9">
         <v>85</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G10">
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -606,7 +613,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>76.666666666666671</v>
+        <v>79.444444444444443</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EE1CF4-6563-4953-ADDA-2D9EE991DAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{38EE1CF4-6563-4953-ADDA-2D9EE991DAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCA14E45-1A87-46E2-8EC7-20FDCB675260}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView minimized="1" xWindow="5220" yWindow="1174" windowWidth="11580" windowHeight="8426" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -440,9 +440,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.28515625" customWidth="1"/>
+    <col min="5" max="6" width="5.3046875" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -487,7 +487,7 @@
         <v>60</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -617,7 +617,7 @@
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{38EE1CF4-6563-4953-ADDA-2D9EE991DAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCA14E45-1A87-46E2-8EC7-20FDCB675260}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A824EC5E-6FFC-4F48-B4A6-BF0AAAD3607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5220" yWindow="1174" windowWidth="11580" windowHeight="8426" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>原</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>下一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -79,17 +83,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -98,11 +111,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -440,33 +456,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.3046875" customWidth="1"/>
+    <col min="5" max="6" width="5.28515625" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="2">
         <v>30</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="2">
         <v>31</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="2">
         <v>1</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="2">
         <v>2</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="2">
         <v>3</v>
+      </c>
+      <c r="J1" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
@@ -496,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -514,7 +533,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -529,7 +548,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -544,7 +563,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -559,7 +578,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -574,7 +593,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -589,7 +608,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="F9">
         <v>85</v>
       </c>
@@ -597,12 +616,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>80</v>
       </c>
     </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
       <c r="E12">
         <f>AVERAGE(E2:E11)</f>
         <v>85</v>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A824EC5E-6FFC-4F48-B4A6-BF0AAAD3607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A824EC5E-6FFC-4F48-B4A6-BF0AAAD3607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79465F31-A007-4E36-845B-12D1D27900BD}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -456,13 +456,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.28515625" customWidth="1"/>
+    <col min="5" max="6" width="5.3046875" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="16.3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -532,8 +532,11 @@
       <c r="G3">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="H3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -547,8 +550,11 @@
       <c r="G4" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="H4" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -563,7 +569,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -578,7 +584,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -593,7 +599,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -608,7 +614,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="F9">
         <v>85</v>
       </c>
@@ -616,7 +622,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>80</v>
       </c>
@@ -640,7 +646,7 @@
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>78.333333333333329</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A824EC5E-6FFC-4F48-B4A6-BF0AAAD3607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79465F31-A007-4E36-845B-12D1D27900BD}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A824EC5E-6FFC-4F48-B4A6-BF0AAAD3607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15288766-1CC3-4AC9-9EAF-25B82A9333F4}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -509,7 +509,7 @@
         <v>80</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -566,6 +566,9 @@
         <v>78</v>
       </c>
       <c r="G5">
+        <v>85</v>
+      </c>
+      <c r="H5">
         <v>85</v>
       </c>
     </row>
@@ -646,11 +649,11 @@
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>78.333333333333329</v>
+        <v>80</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A824EC5E-6FFC-4F48-B4A6-BF0AAAD3607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15288766-1CC3-4AC9-9EAF-25B82A9333F4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9194168D-76D2-49C7-99BA-56BE4300A275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -456,13 +456,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.3046875" customWidth="1"/>
+    <col min="5" max="6" width="5.28515625" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="16.350000000000001" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -535,8 +535,11 @@
       <c r="H3">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="I3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -553,8 +556,11 @@
       <c r="H4" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="I4" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -572,7 +578,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -587,7 +593,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -602,7 +608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -617,7 +623,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="F9">
         <v>85</v>
       </c>
@@ -625,7 +631,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>80</v>
       </c>
@@ -653,7 +659,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9194168D-76D2-49C7-99BA-56BE4300A275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9194168D-76D2-49C7-99BA-56BE4300A275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE8DB50-4CD5-4651-9091-F9FEBB3D209F}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -456,13 +456,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.28515625" customWidth="1"/>
+    <col min="5" max="6" width="5.3046875" customWidth="1"/>
     <col min="7" max="10" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.350000000000001" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="16.399999999999999" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -515,7 +515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -539,7 +539,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -560,7 +560,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -577,8 +577,11 @@
       <c r="H5">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="I5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -593,7 +596,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -608,7 +611,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -623,7 +626,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="F9">
         <v>85</v>
       </c>
@@ -631,7 +634,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>80</v>
       </c>
@@ -659,7 +662,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9194168D-76D2-49C7-99BA-56BE4300A275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE8DB50-4CD5-4651-9091-F9FEBB3D209F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFBB67D-6157-4DE1-B17E-3791E76F5FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -455,14 +455,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="6" width="5.3046875" customWidth="1"/>
-    <col min="7" max="10" width="5" customWidth="1"/>
+    <col min="5" max="8" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -470,25 +469,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G1" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1" s="2">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2">
-        <v>3</v>
-      </c>
-      <c r="J1" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.399999999999999" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -497,25 +490,19 @@
         <v>64</v>
       </c>
       <c r="E2">
+        <v>60</v>
+      </c>
+      <c r="F2">
         <v>80</v>
       </c>
-      <c r="F2">
-        <v>75</v>
-      </c>
       <c r="G2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>80</v>
-      </c>
-      <c r="I2">
-        <v>90</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -527,19 +514,16 @@
         <v>90</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H3">
-        <v>80</v>
-      </c>
-      <c r="I3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -547,20 +531,17 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
+      <c r="E4" s="1">
+        <v>65</v>
+      </c>
       <c r="F4" s="1">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G4" s="1">
-        <v>65</v>
-      </c>
-      <c r="H4" s="1">
-        <v>75</v>
-      </c>
-      <c r="I4" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -568,20 +549,17 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
+      <c r="E5">
+        <v>85</v>
+      </c>
       <c r="F5">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G5">
-        <v>85</v>
-      </c>
-      <c r="H5">
-        <v>85</v>
-      </c>
-      <c r="I5">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -589,14 +567,11 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6">
+      <c r="E6">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -604,14 +579,11 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="F7">
+      <c r="E7">
         <v>90</v>
       </c>
-      <c r="G7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -619,50 +591,40 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="F8">
+      <c r="E8">
         <v>75</v>
       </c>
-      <c r="G8">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="F9">
-        <v>85</v>
-      </c>
-      <c r="G9">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E9">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="G10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E10">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12">
-        <f>AVERAGE(E2:E11)</f>
-        <v>85</v>
+        <f t="shared" ref="E12:H12" si="1">AVERAGE(E2:E11)</f>
+        <v>79.444444444444443</v>
       </c>
       <c r="F12">
-        <f t="shared" ref="F12:I12" si="1">AVERAGE(F2:F11)</f>
-        <v>79.125</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>79.444444444444443</v>
+        <v>82.5</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFBB67D-6157-4DE1-B17E-3791E76F5FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E80B62B-1B9B-4EC9-B2B2-FFC495B6CBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -540,6 +540,9 @@
       <c r="G4" s="1">
         <v>85</v>
       </c>
+      <c r="H4" s="1">
+        <v>70</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -557,6 +560,9 @@
       </c>
       <c r="G5">
         <v>75</v>
+      </c>
+      <c r="H5">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
@@ -624,7 +630,7 @@
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E80B62B-1B9B-4EC9-B2B2-FFC495B6CBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B08827-324C-4735-8B0A-73A713C8DB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -455,13 +455,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="8" width="5" customWidth="1"/>
+    <col min="9" max="11" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -480,8 +481,11 @@
       <c r="H1" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I1" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -502,7 +506,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -523,7 +527,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -544,7 +548,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -565,7 +569,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -576,8 +580,11 @@
       <c r="E6">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="H6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -589,7 +596,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -601,18 +608,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E9">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E10">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
@@ -630,7 +637,7 @@
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B08827-324C-4735-8B0A-73A713C8DB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0692DDA7-65C5-4CFD-B7E0-2CF31752618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -455,14 +455,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="8" width="5" customWidth="1"/>
-    <col min="9" max="11" width="4.5" customWidth="1"/>
+    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="5" max="7" width="5" customWidth="1"/>
+    <col min="8" max="10" width="4.4609375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -470,22 +471,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1" s="2">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -494,19 +492,19 @@
         <v>64</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F2">
+        <v>90</v>
+      </c>
+      <c r="G2">
+        <v>95</v>
+      </c>
+      <c r="H2">
         <v>80</v>
       </c>
-      <c r="G2">
-        <v>90</v>
-      </c>
-      <c r="H2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -515,19 +513,19 @@
         <v>66</v>
       </c>
       <c r="E3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F3">
         <v>80</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H3">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -536,19 +534,16 @@
         <v>68</v>
       </c>
       <c r="E4" s="1">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G4" s="1">
-        <v>85</v>
-      </c>
-      <c r="H4" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -560,16 +555,13 @@
         <v>85</v>
       </c>
       <c r="F5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G5">
-        <v>75</v>
-      </c>
-      <c r="H5">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -577,14 +569,11 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="E6">
-        <v>70</v>
-      </c>
-      <c r="H6">
+      <c r="G6">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -592,11 +581,8 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="E7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -604,40 +590,27 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="E8">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="E9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="E10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:8" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12">
         <f t="shared" ref="E12:H12" si="1">AVERAGE(E2:E11)</f>
-        <v>79.444444444444443</v>
+        <v>80</v>
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>83</v>
       </c>
       <c r="H12">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0692DDA7-65C5-4CFD-B7E0-2CF31752618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F47EF00-9A7D-4614-940A-35480D6851F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -542,6 +542,9 @@
       <c r="G4" s="1">
         <v>70</v>
       </c>
+      <c r="H4" s="1">
+        <v>95</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -559,6 +562,9 @@
       </c>
       <c r="G5">
         <v>80</v>
+      </c>
+      <c r="H5">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F47EF00-9A7D-4614-940A-35480D6851F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8105D1-7CF8-45C7-8203-9B06D4786162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -455,15 +455,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="4" max="4" width="5.640625" customWidth="1"/>
     <col min="5" max="7" width="5" customWidth="1"/>
-    <col min="8" max="10" width="4.4609375" customWidth="1"/>
+    <col min="8" max="10" width="4.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -482,8 +482,11 @@
       <c r="H1" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I1" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -503,8 +506,11 @@
       <c r="H2">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -524,8 +530,11 @@
       <c r="H3">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="I3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -546,7 +555,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -567,7 +576,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -579,7 +588,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -588,7 +597,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -597,8 +606,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8105D1-7CF8-45C7-8203-9B06D4786162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC9FA4-AC7E-43E9-BD39-B2E1E87AFEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -554,6 +554,9 @@
       <c r="H4" s="1">
         <v>95</v>
       </c>
+      <c r="I4" s="1">
+        <v>70</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -612,7 +615,7 @@
         <v>2</v>
       </c>
       <c r="E12">
-        <f t="shared" ref="E12:H12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:I12" si="1">AVERAGE(E2:E11)</f>
         <v>80</v>
       </c>
       <c r="F12">
@@ -626,6 +629,10 @@
       <c r="H12">
         <f t="shared" si="1"/>
         <v>82.5</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CC9FA4-AC7E-43E9-BD39-B2E1E87AFEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53491AFB-E268-4F7D-B369-0D393ADB525F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -578,6 +578,9 @@
       <c r="H5">
         <v>70</v>
       </c>
+      <c r="I5">
+        <v>85</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -632,7 +635,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>77.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53491AFB-E268-4F7D-B369-0D393ADB525F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF53D84F-B142-4C12-86CF-F19462559DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.640625" customWidth="1"/>
@@ -463,7 +463,7 @@
     <col min="8" max="10" width="4.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -485,8 +485,11 @@
       <c r="I1" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J1" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -510,7 +513,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -534,7 +537,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -558,7 +561,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -582,7 +585,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -593,8 +596,11 @@
       <c r="G6">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="I6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -603,7 +609,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -612,8 +618,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
@@ -635,7 +641,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>77.5</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF53D84F-B142-4C12-86CF-F19462559DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB42A3C-481A-40F8-AF2C-80ED58F84220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -608,6 +608,9 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -641,7 +644,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>79</v>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB42A3C-481A-40F8-AF2C-80ED58F84220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75DF79D-3E1B-491A-BDE9-C0A86249C9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -620,6 +620,9 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
+      <c r="I8">
+        <v>75</v>
+      </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -644,7 +647,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>81.428571428571431</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75DF79D-3E1B-491A-BDE9-C0A86249C9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C9B69E-D087-43A9-82F0-373631A6EACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -624,6 +624,11 @@
         <v>75</v>
       </c>
     </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="I9">
+        <v>75</v>
+      </c>
+    </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
@@ -647,7 +652,7 @@
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>81.428571428571431</v>
+        <v>80.625</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C9B69E-D087-43A9-82F0-373631A6EACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D99B02-AB88-4048-BF12-470686DB3C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -512,6 +512,9 @@
       <c r="I2">
         <v>80</v>
       </c>
+      <c r="J2">
+        <v>85</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D99B02-AB88-4048-BF12-470686DB3C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -539,6 +539,9 @@
       <c r="I3">
         <v>75</v>
       </c>
+      <c r="J3">
+        <v>90</v>
+      </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
@@ -562,6 +565,9 @@
       </c>
       <c r="I4" s="1">
         <v>70</v>
+      </c>
+      <c r="J4" s="1">
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
@@ -638,7 +644,7 @@
         <v>2</v>
       </c>
       <c r="E12">
-        <f t="shared" ref="E12:I12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
         <v>80</v>
       </c>
       <c r="F12">
@@ -656,6 +662,10 @@
       <c r="I12">
         <f t="shared" si="1"/>
         <v>80.625</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>86.666666666666671</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB1B3CEC-A6CF-4D74-B4AB-37A410A73D9C}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -136,6 +136,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,15 +459,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.640625" customWidth="1"/>
+    <col min="4" max="4" width="5.61328125" customWidth="1"/>
     <col min="5" max="7" width="5" customWidth="1"/>
-    <col min="8" max="10" width="4.42578125" customWidth="1"/>
+    <col min="8" max="10" width="4.3828125" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,8 +493,11 @@
       <c r="J1" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="K1" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -516,7 +524,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -543,7 +551,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -570,7 +578,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -593,8 +601,11 @@
       <c r="I5">
         <v>85</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -608,8 +619,11 @@
       <c r="I6">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -620,8 +634,11 @@
       <c r="I7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -633,13 +650,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" ht="16.3" x14ac:dyDescent="0.45">
       <c r="I9">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
@@ -665,7 +682,7 @@
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
-        <v>86.666666666666671</v>
+        <v>85.833333333333329</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB1B3CEC-A6CF-4D74-B4AB-37A410A73D9C}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E264153-82DE-485F-A69D-2D12237F78E5}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -111,7 +111,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -119,6 +119,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,6 +526,9 @@
       <c r="J2">
         <v>85</v>
       </c>
+      <c r="K2">
+        <v>90</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
@@ -550,6 +556,9 @@
       <c r="J3">
         <v>90</v>
       </c>
+      <c r="K3">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
@@ -577,6 +586,9 @@
       <c r="J4" s="1">
         <v>85</v>
       </c>
+      <c r="K4" s="1">
+        <v>95</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -604,6 +616,9 @@
       <c r="J5">
         <v>85</v>
       </c>
+      <c r="K5">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -648,6 +663,9 @@
       </c>
       <c r="I8">
         <v>75</v>
+      </c>
+      <c r="J8">
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.3" x14ac:dyDescent="0.45">
@@ -660,29 +678,33 @@
       <c r="D12" t="s">
         <v>2</v>
       </c>
-      <c r="E12">
-        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
+      <c r="E12" s="3">
+        <f t="shared" ref="E12:K12" si="1">AVERAGE(E2:E11)</f>
         <v>80</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <f t="shared" si="1"/>
         <v>82.5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <f t="shared" si="1"/>
         <v>82.5</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="3">
         <f t="shared" si="1"/>
         <v>80.625</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>85.833333333333329</v>
+        <v>86.428571428571431</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>86.25</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E264153-82DE-485F-A69D-2D12237F78E5}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D117033-E1CA-49EE-B67F-DC7B6A1AF341}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -462,16 +462,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.61328125" customWidth="1"/>
-    <col min="5" max="7" width="5" customWidth="1"/>
-    <col min="8" max="10" width="4.3828125" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" customWidth="1"/>
+    <col min="5" max="6" width="5" customWidth="1"/>
+    <col min="7" max="9" width="4.3828125" customWidth="1"/>
+    <col min="10" max="10" width="4.69140625" customWidth="1"/>
+    <col min="11" max="13" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -479,28 +480,25 @@
         <v>1</v>
       </c>
       <c r="E1" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" s="2">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -509,28 +507,25 @@
         <v>64</v>
       </c>
       <c r="E2">
+        <v>90</v>
+      </c>
+      <c r="F2">
+        <v>95</v>
+      </c>
+      <c r="G2">
         <v>80</v>
-      </c>
-      <c r="F2">
-        <v>90</v>
-      </c>
-      <c r="G2">
-        <v>95</v>
       </c>
       <c r="H2">
         <v>80</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J2">
-        <v>85</v>
-      </c>
-      <c r="K2">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -542,25 +537,22 @@
         <v>80</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G3">
         <v>85</v>
       </c>
       <c r="H3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J3">
-        <v>90</v>
-      </c>
-      <c r="K3">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -569,28 +561,25 @@
         <v>68</v>
       </c>
       <c r="E4" s="1">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F4" s="1">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G4" s="1">
+        <v>95</v>
+      </c>
+      <c r="H4" s="1">
         <v>70</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
+        <v>85</v>
+      </c>
+      <c r="J4" s="1">
         <v>95</v>
       </c>
-      <c r="I4" s="1">
-        <v>70</v>
-      </c>
-      <c r="J4" s="1">
-        <v>85</v>
-      </c>
-      <c r="K4" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -599,28 +588,25 @@
         <v>70</v>
       </c>
       <c r="E5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I5">
         <v>85</v>
       </c>
       <c r="J5">
-        <v>85</v>
-      </c>
-      <c r="K5">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -628,17 +614,20 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="G6">
+      <c r="F6">
+        <v>85</v>
+      </c>
+      <c r="H6">
         <v>85</v>
       </c>
       <c r="I6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J6">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -646,14 +635,14 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
       <c r="I7">
-        <v>100</v>
-      </c>
-      <c r="J7">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -661,50 +650,46 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
+      <c r="H8">
+        <v>75</v>
+      </c>
       <c r="I8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="H9">
         <v>75</v>
       </c>
-      <c r="J8">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="16.3" x14ac:dyDescent="0.45">
-      <c r="I9">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:K12" si="1">AVERAGE(E2:E11)</f>
-        <v>80</v>
+        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
+        <v>82.5</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>80.625</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>80.625</v>
+        <v>86.428571428571431</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>86.428571428571431</v>
-      </c>
-      <c r="K12" s="3">
-        <f t="shared" si="1"/>
-        <v>86.25</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D117033-E1CA-49EE-B67F-DC7B6A1AF341}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA745ECE-CB6D-44E9-9DE1-BF9209ED8F61}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -462,17 +462,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.61328125" customWidth="1"/>
-    <col min="5" max="6" width="5" customWidth="1"/>
-    <col min="7" max="9" width="4.3828125" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" customWidth="1"/>
-    <col min="11" max="13" width="5" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="6" max="8" width="4.3828125" customWidth="1"/>
+    <col min="9" max="9" width="4.69140625" customWidth="1"/>
+    <col min="10" max="12" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -480,25 +480,22 @@
         <v>1</v>
       </c>
       <c r="E1" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -507,25 +504,22 @@
         <v>64</v>
       </c>
       <c r="E2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G2">
         <v>80</v>
       </c>
       <c r="H2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I2">
-        <v>85</v>
-      </c>
-      <c r="J2">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -534,25 +528,22 @@
         <v>66</v>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F3">
         <v>85</v>
       </c>
       <c r="G3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I3">
-        <v>90</v>
-      </c>
-      <c r="J3">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -561,25 +552,22 @@
         <v>68</v>
       </c>
       <c r="E4" s="1">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F4" s="1">
+        <v>95</v>
+      </c>
+      <c r="G4" s="1">
         <v>70</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
+        <v>85</v>
+      </c>
+      <c r="I4" s="1">
         <v>95</v>
       </c>
-      <c r="H4" s="1">
-        <v>70</v>
-      </c>
-      <c r="I4" s="1">
-        <v>85</v>
-      </c>
-      <c r="J4" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -588,25 +576,22 @@
         <v>70</v>
       </c>
       <c r="E5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H5">
         <v>85</v>
       </c>
       <c r="I5">
-        <v>85</v>
-      </c>
-      <c r="J5">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -614,20 +599,20 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="F6">
+      <c r="E6">
+        <v>85</v>
+      </c>
+      <c r="G6">
         <v>85</v>
       </c>
       <c r="H6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I6">
         <v>75</v>
       </c>
-      <c r="J6">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -635,14 +620,17 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
+      <c r="G7">
+        <v>100</v>
+      </c>
       <c r="H7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I7">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -650,46 +638,42 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
       <c r="H8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G9">
         <v>75</v>
       </c>
-      <c r="I8">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="H9">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
-        <v>82.5</v>
+        <f t="shared" ref="E12:I12" si="1">AVERAGE(E2:E11)</f>
+        <v>83</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>80.625</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>80.625</v>
+        <v>86.428571428571431</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>86.428571428571431</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="1"/>
-        <v>84</v>
+        <v>85.833333333333329</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA745ECE-CB6D-44E9-9DE1-BF9209ED8F61}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA2B2241-A9AD-4A80-97D8-431D5986F02D}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.61328125" customWidth="1"/>
@@ -472,7 +472,7 @@
     <col min="10" max="12" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -494,8 +494,11 @@
       <c r="I1" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -519,7 +522,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -543,7 +546,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -567,7 +570,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -591,7 +594,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -612,7 +615,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -630,7 +633,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -644,14 +647,17 @@
       <c r="H8">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I8">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
@@ -673,7 +679,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>85.833333333333329</v>
+        <v>84.285714285714292</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{64B431DC-B3C8-488C-800B-189D05D87F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA2B2241-A9AD-4A80-97D8-431D5986F02D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7ADDB7D-4868-480F-96C9-44782E377474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -139,10 +139,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -463,16 +459,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="4" max="4" width="5.640625" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="8" width="4.3828125" customWidth="1"/>
-    <col min="9" max="9" width="4.69140625" customWidth="1"/>
+    <col min="6" max="8" width="4.35546875" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="12" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -498,7 +494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -521,8 +517,11 @@
       <c r="I2">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -546,7 +545,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -570,7 +569,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -594,7 +593,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -615,7 +614,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -633,7 +632,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -651,7 +650,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>75</v>
       </c>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7ADDB7D-4868-480F-96C9-44782E377474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225E9845-8A74-439E-86FD-DE3677A4BEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.640625" customWidth="1"/>
@@ -468,7 +468,7 @@
     <col min="10" max="12" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -494,7 +494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -521,7 +521,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -544,8 +544,11 @@
       <c r="I3">
         <v>95</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -569,7 +572,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -593,7 +596,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -614,7 +617,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -632,7 +635,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -650,18 +653,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:I12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:L12" si="1">AVERAGE(E2:E11)</f>
         <v>83</v>
       </c>
       <c r="F12" s="3">
@@ -680,6 +683,12 @@
         <f t="shared" si="1"/>
         <v>84.285714285714292</v>
       </c>
+      <c r="J12" s="3">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225E9845-8A74-439E-86FD-DE3677A4BEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18490EC1-F3C3-4EBF-AF81-81960331B560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -493,6 +493,12 @@
       <c r="J1" s="2">
         <v>9</v>
       </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
@@ -570,6 +576,9 @@
       </c>
       <c r="I4" s="1">
         <v>95</v>
+      </c>
+      <c r="J4" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
@@ -685,7 +694,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>78.333333333333329</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18490EC1-F3C3-4EBF-AF81-81960331B560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -604,6 +604,9 @@
       <c r="I5">
         <v>65</v>
       </c>
+      <c r="J5">
+        <v>85</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -694,7 +697,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>78.333333333333329</v>
+        <v>80</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6793BA17-72EF-4412-8B9B-10B66F8A9C8A}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -459,16 +459,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.640625" customWidth="1"/>
+    <col min="4" max="4" width="5.61328125" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="8" width="4.35546875" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="6" max="8" width="4.3828125" customWidth="1"/>
+    <col min="9" max="9" width="4.69140625" customWidth="1"/>
     <col min="10" max="12" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -500,7 +500,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -527,7 +527,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -554,7 +554,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -581,7 +581,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -608,7 +608,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -628,8 +628,11 @@
       <c r="I6">
         <v>75</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -646,8 +649,11 @@
       <c r="I7">
         <v>95</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -665,7 +671,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>75</v>
       </c>
@@ -676,7 +682,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:L12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
         <v>83</v>
       </c>
       <c r="F12" s="3">
@@ -697,7 +703,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>81.666666666666671</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6793BA17-72EF-4412-8B9B-10B66F8A9C8A}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11155320-5FEA-44CD-B4DD-239E3032F4AC}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -670,6 +670,9 @@
       <c r="I8">
         <v>75</v>
       </c>
+      <c r="J8">
+        <v>85</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="G9">
@@ -703,7 +706,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>81.666666666666671</v>
+        <v>82.142857142857139</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11155320-5FEA-44CD-B4DD-239E3032F4AC}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E89E8A8-16DD-488A-B56A-C0999F0700E8}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -678,6 +678,9 @@
       <c r="G9">
         <v>75</v>
       </c>
+      <c r="J9">
+        <v>90</v>
+      </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
@@ -706,7 +709,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>82.142857142857139</v>
+        <v>83.125</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E89E8A8-16DD-488A-B56A-C0999F0700E8}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9A04FE-63CE-4946-89B5-569240B8E6D0}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9A04FE-63CE-4946-89B5-569240B8E6D0}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5A6A0B5-4022-4AE0-9639-5A69460DCA40}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -682,6 +682,11 @@
         <v>90</v>
       </c>
     </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="J10">
+        <v>85</v>
+      </c>
+    </row>
     <row r="11" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
@@ -709,7 +714,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>83.125</v>
+        <v>83.333333333333329</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5A6A0B5-4022-4AE0-9639-5A69460DCA40}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F270AE3-BB2F-44CA-815C-B1D8310EBDB1}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -687,7 +687,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="J11" s="2">
+        <v>75</v>
+      </c>
+    </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
@@ -714,7 +718,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>83.333333333333329</v>
+        <v>82.5</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F270AE3-BB2F-44CA-815C-B1D8310EBDB1}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9471E40D-562B-4543-9490-E44CF24DCA3D}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -526,6 +526,9 @@
       <c r="J2">
         <v>90</v>
       </c>
+      <c r="K2">
+        <v>80</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9471E40D-562B-4543-9490-E44CF24DCA3D}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F76C87B8-CDE0-4BD4-88E3-6D07A522BBBF}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -556,6 +556,9 @@
       <c r="J3">
         <v>70</v>
       </c>
+      <c r="K3">
+        <v>85</v>
+      </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
@@ -700,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:K12" si="1">AVERAGE(E2:E11)</f>
         <v>83</v>
       </c>
       <c r="F12" s="3">
@@ -723,7 +726,10 @@
         <f t="shared" si="1"/>
         <v>82.5</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>82.5</v>
+      </c>
       <c r="L12" s="3"/>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F76C87B8-CDE0-4BD4-88E3-6D07A522BBBF}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59524FED-04F3-4D44-895D-717CC4CC6E4F}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -586,6 +586,9 @@
       <c r="J4" s="1">
         <v>75</v>
       </c>
+      <c r="K4" s="1">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -728,7 +731,7 @@
       </c>
       <c r="K12" s="3">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>83.333333333333329</v>
       </c>
       <c r="L12" s="3"/>
     </row>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59524FED-04F3-4D44-895D-717CC4CC6E4F}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5D8D7B-6BEC-46BA-8117-AB512B3A1A38}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -616,6 +616,9 @@
       <c r="J5">
         <v>85</v>
       </c>
+      <c r="K5">
+        <v>90</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -731,7 +734,7 @@
       </c>
       <c r="K12" s="3">
         <f t="shared" si="1"/>
-        <v>83.333333333333329</v>
+        <v>85</v>
       </c>
       <c r="L12" s="3"/>
     </row>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5D8D7B-6BEC-46BA-8117-AB512B3A1A38}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D22F466-297A-497E-B874-3E5631084322}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -643,6 +643,9 @@
       <c r="J6">
         <v>80</v>
       </c>
+      <c r="K6">
+        <v>85</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{E679EE83-0F1F-4116-81F1-CECEF082C810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D22F466-297A-497E-B874-3E5631084322}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D234C75-C156-459B-BD34-365CCDD5A75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -458,17 +458,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.61328125" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="8" width="4.3828125" customWidth="1"/>
-    <col min="9" max="9" width="4.69140625" customWidth="1"/>
-    <col min="10" max="12" width="5" customWidth="1"/>
+    <col min="4" max="4" width="5.640625" customWidth="1"/>
+    <col min="5" max="7" width="4.35546875" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="11" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -476,31 +475,28 @@
         <v>1</v>
       </c>
       <c r="E1" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="2">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -509,28 +505,25 @@
         <v>64</v>
       </c>
       <c r="E2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="F2">
         <v>80</v>
       </c>
       <c r="G2">
+        <v>85</v>
+      </c>
+      <c r="H2">
+        <v>90</v>
+      </c>
+      <c r="I2">
+        <v>90</v>
+      </c>
+      <c r="J2">
         <v>80</v>
       </c>
-      <c r="H2">
-        <v>85</v>
-      </c>
-      <c r="I2">
-        <v>90</v>
-      </c>
-      <c r="J2">
-        <v>90</v>
-      </c>
-      <c r="K2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -542,25 +535,22 @@
         <v>85</v>
       </c>
       <c r="F3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I3">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="J3">
-        <v>70</v>
-      </c>
-      <c r="K3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -569,28 +559,25 @@
         <v>68</v>
       </c>
       <c r="E4" s="1">
+        <v>95</v>
+      </c>
+      <c r="F4" s="1">
         <v>70</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
+        <v>85</v>
+      </c>
+      <c r="H4" s="1">
         <v>95</v>
       </c>
-      <c r="G4" s="1">
-        <v>70</v>
-      </c>
-      <c r="H4" s="1">
-        <v>85</v>
-      </c>
       <c r="I4" s="1">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J4" s="1">
-        <v>75</v>
-      </c>
-      <c r="K4" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -599,28 +586,25 @@
         <v>70</v>
       </c>
       <c r="E5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G5">
         <v>85</v>
       </c>
       <c r="H5">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I5">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J5">
-        <v>85</v>
-      </c>
-      <c r="K5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -628,26 +612,23 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>85</v>
       </c>
       <c r="G6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H6">
         <v>75</v>
       </c>
       <c r="I6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>80</v>
-      </c>
-      <c r="K6">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -655,20 +636,23 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
       <c r="G7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H7">
         <v>95</v>
       </c>
       <c r="I7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J7">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -676,70 +660,66 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
+      <c r="F8">
+        <v>75</v>
+      </c>
       <c r="G8">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I8">
-        <v>75</v>
-      </c>
-      <c r="J8">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="G9">
-        <v>75</v>
-      </c>
-      <c r="J9">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="J10">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="J11" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="F9">
+        <v>75</v>
+      </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="I10">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="I11" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:K12" si="1">AVERAGE(E2:E11)</f>
-        <v>83</v>
+        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
+        <v>82.5</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>80.625</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="1"/>
-        <v>80.625</v>
+        <v>86.428571428571431</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>86.428571428571431</v>
+        <v>84.285714285714292</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>84.285714285714292</v>
+        <v>82.5</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>82.5</v>
-      </c>
-      <c r="K12" s="3">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="L12" s="3"/>
+        <v>85.833333333333329</v>
+      </c>
+      <c r="K12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D234C75-C156-459B-BD34-365CCDD5A75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E521AD0-90F6-461F-9CAD-3B625D89F7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -672,6 +672,9 @@
       <c r="I8">
         <v>85</v>
       </c>
+      <c r="J8">
+        <v>90</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="F9">
@@ -717,7 +720,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>85.833333333333329</v>
+        <v>86.428571428571431</v>
       </c>
       <c r="K12" s="3"/>
     </row>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E521AD0-90F6-461F-9CAD-3B625D89F7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AE9C55-C8F7-46BC-96BC-FD0C997373E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -683,6 +683,9 @@
       <c r="I9">
         <v>90</v>
       </c>
+      <c r="J9">
+        <v>80</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="I10">
@@ -720,7 +723,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>86.428571428571431</v>
+        <v>85.625</v>
       </c>
       <c r="K12" s="3"/>
     </row>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AE9C55-C8F7-46BC-96BC-FD0C997373E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -691,6 +691,9 @@
       <c r="I10">
         <v>85</v>
       </c>
+      <c r="J10">
+        <v>80</v>
+      </c>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="I11" s="2">
@@ -723,7 +726,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>85.625</v>
+        <v>85</v>
       </c>
       <c r="K12" s="3"/>
     </row>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19FEB1A9-6714-42AB-94A8-FBF6DC5E12B4}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -458,16 +458,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.640625" customWidth="1"/>
-    <col min="5" max="7" width="4.35546875" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="11" width="5" customWidth="1"/>
+    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="5" max="5" width="4.3828125" customWidth="1"/>
+    <col min="6" max="6" width="4.69140625" customWidth="1"/>
+    <col min="7" max="9" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -475,28 +475,22 @@
         <v>1</v>
       </c>
       <c r="E1" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F1" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H1" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I1" s="2">
-        <v>9</v>
-      </c>
-      <c r="J1" s="2">
-        <v>10</v>
-      </c>
-      <c r="K1" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -505,25 +499,19 @@
         <v>64</v>
       </c>
       <c r="E2">
+        <v>85</v>
+      </c>
+      <c r="F2">
+        <v>90</v>
+      </c>
+      <c r="G2">
+        <v>90</v>
+      </c>
+      <c r="H2">
         <v>80</v>
       </c>
-      <c r="F2">
-        <v>80</v>
-      </c>
-      <c r="G2">
-        <v>85</v>
-      </c>
-      <c r="H2">
-        <v>90</v>
-      </c>
-      <c r="I2">
-        <v>90</v>
-      </c>
-      <c r="J2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -532,25 +520,19 @@
         <v>66</v>
       </c>
       <c r="E3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H3">
-        <v>95</v>
-      </c>
-      <c r="I3">
-        <v>70</v>
-      </c>
-      <c r="J3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -559,25 +541,19 @@
         <v>68</v>
       </c>
       <c r="E4" s="1">
+        <v>85</v>
+      </c>
+      <c r="F4" s="1">
         <v>95</v>
       </c>
-      <c r="F4" s="1">
-        <v>70</v>
-      </c>
       <c r="G4" s="1">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H4" s="1">
-        <v>95</v>
-      </c>
-      <c r="I4" s="1">
-        <v>75</v>
-      </c>
-      <c r="J4" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -586,25 +562,19 @@
         <v>70</v>
       </c>
       <c r="E5">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F5">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>85</v>
       </c>
       <c r="H5">
-        <v>65</v>
-      </c>
-      <c r="I5">
-        <v>85</v>
-      </c>
-      <c r="J5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -612,23 +582,20 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
       <c r="F6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>75</v>
-      </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -636,23 +603,20 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
+      <c r="E7">
+        <v>95</v>
+      </c>
       <c r="F7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H7">
-        <v>95</v>
-      </c>
-      <c r="I7">
-        <v>90</v>
-      </c>
-      <c r="J7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -660,75 +624,64 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
       <c r="F8">
         <v>75</v>
       </c>
       <c r="G8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G9">
+        <v>90</v>
+      </c>
+      <c r="H9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="G10">
+        <v>85</v>
+      </c>
+      <c r="H10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G11" s="2">
         <v>75</v>
       </c>
-      <c r="I8">
-        <v>85</v>
-      </c>
-      <c r="J8">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="F9">
-        <v>75</v>
-      </c>
-      <c r="I9">
-        <v>90</v>
-      </c>
-      <c r="J9">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="I10">
-        <v>85</v>
-      </c>
-      <c r="J10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="I11" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="H11" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
-        <v>82.5</v>
+        <f t="shared" ref="E12:H12" si="1">AVERAGE(E2:E11)</f>
+        <v>86.428571428571431</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>80.625</v>
+        <v>84.285714285714292</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="1"/>
-        <v>86.428571428571431</v>
+        <v>82.5</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>84.285714285714292</v>
-      </c>
-      <c r="I12" s="3">
-        <f t="shared" si="1"/>
-        <v>82.5</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="K12" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="I12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19FEB1A9-6714-42AB-94A8-FBF6DC5E12B4}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D21C9DEB-EFC0-45E2-9766-E111BA5A5321}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -510,6 +510,9 @@
       <c r="H2">
         <v>80</v>
       </c>
+      <c r="I2">
+        <v>85</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D21C9DEB-EFC0-45E2-9766-E111BA5A5321}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EEADCDC-0D7D-4B5B-983D-8FC6610C339F}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -534,6 +534,9 @@
       <c r="H3">
         <v>85</v>
       </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EEADCDC-0D7D-4B5B-983D-8FC6610C339F}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54AC1EFB-436F-4DE4-8CF8-9F44F7824827}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -558,6 +558,9 @@
       <c r="H4" s="1">
         <v>85</v>
       </c>
+      <c r="I4" s="1">
+        <v>80</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -672,7 +675,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:H12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:I12" si="1">AVERAGE(E2:E11)</f>
         <v>86.428571428571431</v>
       </c>
       <c r="F12" s="3">
@@ -687,7 +690,10 @@
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="I12" s="3"/>
+      <c r="I12" s="3">
+        <f t="shared" si="1"/>
+        <v>88.333333333333329</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54AC1EFB-436F-4DE4-8CF8-9F44F7824827}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C26DFF3D-9536-45D5-A681-FA646133D7E0}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -139,6 +139,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -582,6 +586,9 @@
       <c r="H5">
         <v>90</v>
       </c>
+      <c r="I5">
+        <v>80</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -692,7 +699,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>88.333333333333329</v>
+        <v>86.25</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{3969C258-4B42-4DF1-A6FF-88A4DAC32AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C26DFF3D-9536-45D5-A681-FA646133D7E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D9D7A3-FAE9-4A47-A070-66A2B5680CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -139,10 +139,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -463,15 +459,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.61328125" customWidth="1"/>
-    <col min="5" max="5" width="4.3828125" customWidth="1"/>
-    <col min="6" max="6" width="4.69140625" customWidth="1"/>
+    <col min="4" max="4" width="5.640625" customWidth="1"/>
+    <col min="5" max="5" width="4.35546875" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="9" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -494,7 +490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -518,7 +514,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -542,7 +538,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -566,7 +562,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -590,7 +586,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -610,8 +606,11 @@
       <c r="H6">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -631,8 +630,11 @@
       <c r="H7">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -653,7 +655,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>90</v>
       </c>
@@ -661,7 +663,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>85</v>
       </c>
@@ -699,7 +701,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>86.25</v>
+        <v>86.666666666666671</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D9D7A3-FAE9-4A47-A070-66A2B5680CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5B8D35-B95B-4105-B548-8450EB87D9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -654,6 +654,9 @@
       <c r="H8">
         <v>90</v>
       </c>
+      <c r="I8">
+        <v>95</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
@@ -701,7 +704,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>86.666666666666671</v>
+        <v>87.857142857142861</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5B8D35-B95B-4105-B548-8450EB87D9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4367D1-CBDE-4B4D-AEB6-C978CBEB7F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -665,6 +665,9 @@
       <c r="H9">
         <v>80</v>
       </c>
+      <c r="I9">
+        <v>90</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G10">
@@ -672,6 +675,9 @@
       </c>
       <c r="H10">
         <v>80</v>
+      </c>
+      <c r="I10">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
@@ -704,7 +710,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>87.857142857142861</v>
+        <v>88.333333333333329</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4367D1-CBDE-4B4D-AEB6-C978CBEB7F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9330551-9D33-4C02-AFC5-F882AF586D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -687,6 +687,9 @@
       <c r="H11" s="2">
         <v>85</v>
       </c>
+      <c r="I11" s="2">
+        <v>85</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
@@ -710,7 +713,7 @@
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
-        <v>88.333333333333329</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9330551-9D33-4C02-AFC5-F882AF586D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358DA984-0024-4A94-B7DA-7D397101F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -458,16 +458,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.640625" customWidth="1"/>
     <col min="5" max="5" width="4.35546875" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="9" width="5" customWidth="1"/>
+    <col min="10" max="10" width="5.2109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -489,8 +490,11 @@
       <c r="I1" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -513,8 +517,11 @@
       <c r="I2">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -538,7 +545,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -562,7 +569,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -586,7 +593,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -610,7 +617,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -634,7 +641,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -658,7 +665,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>90</v>
       </c>
@@ -669,7 +676,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>85</v>
       </c>
@@ -680,7 +687,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="G11" s="2">
         <v>75</v>
       </c>
@@ -691,12 +698,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:I12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
         <v>86.428571428571431</v>
       </c>
       <c r="F12" s="3">
@@ -714,6 +721,10 @@
       <c r="I12" s="3">
         <f t="shared" si="1"/>
         <v>88</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="1"/>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358DA984-0024-4A94-B7DA-7D397101F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6400E75E-BB0D-4754-B0CA-D4C6788808A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -544,6 +544,9 @@
       <c r="I3">
         <v>100</v>
       </c>
+      <c r="J3">
+        <v>90</v>
+      </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
@@ -724,7 +727,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6400E75E-BB0D-4754-B0CA-D4C6788808A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD3882C-3486-4DEE-AB69-2D398ED06A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -571,6 +571,9 @@
       <c r="I4" s="1">
         <v>80</v>
       </c>
+      <c r="J4" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -727,7 +730,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>92.5</v>
+        <v>86.666666666666671</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD3882C-3486-4DEE-AB69-2D398ED06A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39470034-2A9D-4F0C-99F7-862C815E6E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -598,6 +598,9 @@
       <c r="I5">
         <v>80</v>
       </c>
+      <c r="J5">
+        <v>90</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -730,7 +733,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>86.666666666666671</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39470034-2A9D-4F0C-99F7-862C815E6E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EC17C2-9A86-40EF-984B-21888CF2AFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -625,6 +625,9 @@
       <c r="I6">
         <v>80</v>
       </c>
+      <c r="J6">
+        <v>90</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -733,7 +736,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>87.5</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EC17C2-9A86-40EF-984B-21888CF2AFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB5433B-BD83-4225-AB53-2B946462303A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -652,6 +652,9 @@
       <c r="I7">
         <v>95</v>
       </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -676,6 +679,9 @@
       <c r="I8">
         <v>95</v>
       </c>
+      <c r="J8">
+        <v>75</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
@@ -736,7 +742,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>88</v>
+        <v>87.857142857142861</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB5433B-BD83-4225-AB53-2B946462303A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19667D8-3F36-4C86-834D-E3C8D3CB0C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -458,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="5.640625" customWidth="1"/>
@@ -466,9 +466,10 @@
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="5.2109375" customWidth="1"/>
+    <col min="11" max="11" width="5.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -493,8 +494,11 @@
       <c r="J1" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="K1" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -521,7 +525,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -548,7 +552,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -575,7 +579,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -602,7 +606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -629,7 +633,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -656,7 +660,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -683,7 +687,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>90</v>
       </c>
@@ -693,8 +697,11 @@
       <c r="I9">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.75" x14ac:dyDescent="0.45">
+      <c r="J9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>85</v>
       </c>
@@ -705,7 +712,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="G11" s="2">
         <v>75</v>
       </c>
@@ -716,7 +723,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>2</v>
       </c>
@@ -742,7 +749,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>87.857142857142861</v>
+        <v>88.75</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19667D8-3F36-4C86-834D-E3C8D3CB0C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -711,6 +711,9 @@
       <c r="I10">
         <v>90</v>
       </c>
+      <c r="J10">
+        <v>75</v>
+      </c>
     </row>
     <row r="11" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="G11" s="2">
@@ -749,7 +752,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>88.75</v>
+        <v>87.222222222222229</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\drher\OneDrive\文件\GitHub\drher.github.io\salf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB7FB9C-2FED-44DD-B4E3-047C1E298DA5}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="15397" windowHeight="8751" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -459,17 +459,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BC73E5-4EF5-4C60-AE79-69067CC67F5B}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="16.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.75" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="5.640625" customWidth="1"/>
-    <col min="5" max="5" width="4.35546875" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="5.61328125" customWidth="1"/>
+    <col min="5" max="5" width="4.3828125" customWidth="1"/>
+    <col min="6" max="6" width="4.69140625" customWidth="1"/>
     <col min="7" max="9" width="5" customWidth="1"/>
-    <col min="10" max="10" width="5.2109375" customWidth="1"/>
-    <col min="11" max="11" width="5.78515625" customWidth="1"/>
+    <col min="10" max="10" width="5.23046875" customWidth="1"/>
+    <col min="11" max="11" width="5.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="16.649999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>90</v>
       </c>
@@ -525,7 +525,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>85</v>
       </c>
@@ -552,7 +552,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>80</v>
       </c>
@@ -579,7 +579,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>75</v>
       </c>
@@ -606,7 +606,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>70</v>
       </c>
@@ -633,7 +633,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>65</v>
       </c>
@@ -660,7 +660,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>60</v>
       </c>
@@ -687,7 +687,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="G9">
         <v>90</v>
       </c>
@@ -701,7 +701,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="G10">
         <v>85</v>
       </c>
@@ -724,6 +724,9 @@
       </c>
       <c r="I11" s="2">
         <v>85</v>
+      </c>
+      <c r="J11" s="2">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -752,7 +755,7 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
-        <v>87.222222222222229</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB7FB9C-2FED-44DD-B4E3-047C1E298DA5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2833AA1-D270-4130-BDFF-C7EA2038F29B}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -466,7 +466,7 @@
     <col min="6" max="6" width="4.69140625" customWidth="1"/>
     <col min="7" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="5.23046875" customWidth="1"/>
-    <col min="11" max="11" width="5.765625" customWidth="1"/>
+    <col min="11" max="11" width="4.921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="17.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
@@ -524,6 +524,9 @@
       <c r="J2">
         <v>95</v>
       </c>
+      <c r="K2">
+        <v>65</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2833AA1-D270-4130-BDFF-C7EA2038F29B}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F6D576F-BEB6-44D5-9D69-0955CC406D36}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -554,6 +554,9 @@
       <c r="J3">
         <v>90</v>
       </c>
+      <c r="K3">
+        <v>80</v>
+      </c>
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
@@ -737,7 +740,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:J12" si="1">AVERAGE(E2:E11)</f>
+        <f t="shared" ref="E12:K12" si="1">AVERAGE(E2:E11)</f>
         <v>86.428571428571431</v>
       </c>
       <c r="F12" s="3">
@@ -759,6 +762,10 @@
       <c r="J12" s="3">
         <f t="shared" si="1"/>
         <v>85</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>72.5</v>
       </c>
     </row>
   </sheetData>

--- a/salf/及格.xlsx
+++ b/salf/及格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25f5a1833553ad9e/文件/GitHub/drher.github.io/salf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F6D576F-BEB6-44D5-9D69-0955CC406D36}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{299EC85D-1FFC-4F1B-80F8-42944DD30B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661CD1C3-EEAE-431C-B45E-C776BE1C297E}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9463" xr2:uid="{36FCF4E2-D0E9-4591-9DE6-5EDA12986967}"/>
   </bookViews>
@@ -584,6 +584,9 @@
       <c r="J4" s="1">
         <v>75</v>
       </c>
+      <c r="K4" s="1">
+        <v>90</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -765,7 +768,7 @@
       </c>
       <c r="K12" s="3">
         <f t="shared" si="1"/>
-        <v>72.5</v>
+        <v>78.333333333333329</v>
       </c>
     </row>
   </sheetData>
